--- a/src/main/resources/qm/public/resources/qualityCriteriaImportSchema_vi.xlsx
+++ b/src/main/resources/qm/public/resources/qualityCriteriaImportSchema_vi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dungn\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qcadoo_demo\mes\mes-plugins\fti-plugins-qm\src\main\resources\qm\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF341964-E7EF-4F91-9DE3-910A5F35A391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB3AE1E-8908-46DD-AAA6-88D31604B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4005ADB-0ECA-4B65-AC63-34404DD8E1BE}"/>
   </bookViews>
@@ -441,6 +441,14 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{C021B627-5DBE-44C5-86CF-3485A6D17E9A}">
+      <formula1>"Định tính, Định lượng"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{1E3050D4-B76E-484A-B445-A85B4CA35324}">
+      <formula1>"cm, cm2, dam, dm, g, hl, kg, l, m, m2, m3, mm, Nm, pack, pair, pc, set, tank, Y/N"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/src/main/resources/qm/public/resources/qualityCriteriaImportSchema_vi.xlsx
+++ b/src/main/resources/qm/public/resources/qualityCriteriaImportSchema_vi.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\qcadoo_demo\mes\mes-plugins\fti-plugins-qm\src\main\resources\qm\public\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DB3AE1E-8908-46DD-AAA6-88D31604B656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3577978-6B67-41FC-9C77-CA0EB6168832}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B4005ADB-0ECA-4B65-AC63-34404DD8E1BE}"/>
+    <workbookView xWindow="7440" yWindow="3345" windowWidth="21600" windowHeight="11235" xr2:uid="{B4005ADB-0ECA-4B65-AC63-34404DD8E1BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,24 +38,32 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t xml:space="preserve">Mã số </t>
+    <t>Đơn vị</t>
   </si>
   <si>
-    <t>Tên tiêu chí</t>
+    <t xml:space="preserve">Mã chỉ tiêu </t>
   </si>
   <si>
-    <t>Loại tiêu chí</t>
+    <t>Tên chỉ tiêu</t>
   </si>
   <si>
-    <t>Đơn vị</t>
+    <t>Loại chỉ tiêu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -83,8 +91,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,27 +433,27 @@
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1:C1048576" xr:uid="{C021B627-5DBE-44C5-86CF-3485A6D17E9A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C1048576 C1" xr:uid="{C021B627-5DBE-44C5-86CF-3485A6D17E9A}">
       <formula1>"Định tính, Định lượng"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1:D1048576" xr:uid="{1E3050D4-B76E-484A-B445-A85B4CA35324}">
@@ -450,5 +461,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>